--- a/templates/TATA Capital/TATA_Repo_Agency_Template_2026-27.xlsx
+++ b/templates/TATA Capital/TATA_Repo_Agency_Template_2026-27.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachit Goyal\Downloads\audit-report-generator\templates\TATA Capital\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachit Goyal\Downloads\audit-automation-final\templates\TATA Capital\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40C8F76E-7571-41F6-B5E8-3C358552E3E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBC8787E-DE75-4968-B07B-E1A7CFF622E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="732" yWindow="732" windowWidth="13152" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Repo Checklist" sheetId="5" r:id="rId1"/>
@@ -33,8 +33,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -752,14 +750,14 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1148,7 +1146,7 @@
         <v>51</v>
       </c>
       <c r="G3" s="24"/>
-      <c r="H3" s="30"/>
+      <c r="H3" s="29"/>
     </row>
     <row r="4" spans="1:10" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C4" s="21" t="s">
@@ -1174,7 +1172,7 @@
       </c>
       <c r="G5" s="24"/>
     </row>
-    <row r="7" spans="1:10" s="31" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" s="30" customFormat="1" ht="48" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
         <v>0</v>
       </c>
@@ -2021,6 +2019,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:F18"/>
   <sheetFormatPr defaultColWidth="33.42578125" defaultRowHeight="13.8" x14ac:dyDescent="0.2"/>
   <cols>
@@ -2242,13 +2243,13 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="29" t="s">
+      <c r="A10" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="29"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
       <c r="F10" s="1" t="str" cm="1">
         <f t="array" ref="F10">_xlfn.IFS(F9&gt;=80%,B13,F9&gt;=70%,B14,F9&gt;=60%,B15,F9&gt;=50%,B16,F9&lt;=49%,B17)</f>
         <v>A</v>
@@ -2333,17 +2334,16 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="0115396f-2e4a-4d2a-ba9c-df4d17cb71a2" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2586,17 +2586,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="0115396f-2e4a-4d2a-ba9c-df4d17cb71a2" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1497B80-A936-4519-8A3E-617F634A3902}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{811DE56B-2DE6-43EB-9A84-91DE4EA53BF9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="2bc29a05-2ca3-4765-9547-41c11361a102"/>
+    <ds:schemaRef ds:uri="0115396f-2e4a-4d2a-ba9c-df4d17cb71a2"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2621,18 +2631,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{811DE56B-2DE6-43EB-9A84-91DE4EA53BF9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1497B80-A936-4519-8A3E-617F634A3902}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="2bc29a05-2ca3-4765-9547-41c11361a102"/>
-    <ds:schemaRef ds:uri="0115396f-2e4a-4d2a-ba9c-df4d17cb71a2"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>